--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>91.45328768124037</v>
+        <v>14.86115924820156</v>
       </c>
       <c r="D2" t="n">
-        <v>81.21443089902023</v>
+        <v>13.19734502109079</v>
       </c>
       <c r="E2" t="n">
-        <v>7.453925269647391</v>
+        <v>1.2112628563177</v>
       </c>
       <c r="F2" t="n">
-        <v>15.47204377540277</v>
+        <v>2.51420711350295</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.20863171875531</v>
+        <v>11.89640265429774</v>
       </c>
       <c r="D3" t="n">
-        <v>68.09818647710289</v>
+        <v>11.06595530252922</v>
       </c>
       <c r="E3" t="n">
-        <v>7.453925269647391</v>
+        <v>1.2112628563177</v>
       </c>
       <c r="F3" t="n">
-        <v>15.47204377540277</v>
+        <v>2.51420711350295</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>81.71948175876483</v>
+        <v>13.27941578579929</v>
       </c>
       <c r="D4" t="n">
-        <v>43.86342439892262</v>
+        <v>7.127806464824926</v>
       </c>
       <c r="E4" t="n">
-        <v>7.453925269647391</v>
+        <v>1.2112628563177</v>
       </c>
       <c r="F4" t="n">
-        <v>15.47204377540277</v>
+        <v>2.51420711350295</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
